--- a/results/metrics_ud.xlsx
+++ b/results/metrics_ud.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dalhousie\Desktop\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD77556D-B7E7-4192-B72B-8669A44F6363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B70D34-907D-4108-ABB4-8EA75AE643C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CEF30AF1-C0FA-444E-A5F8-C0020D3AD9A8}"/>
   </bookViews>
@@ -5911,6 +5911,9 @@
       <c r="D2" t="s">
         <v>66</v>
       </c>
+      <c r="E2" s="3">
+        <v>1596</v>
+      </c>
       <c r="F2" s="3">
         <v>0</v>
       </c>
@@ -5940,6 +5943,9 @@
       <c r="D3" t="s">
         <v>188</v>
       </c>
+      <c r="E3" s="3">
+        <v>855</v>
+      </c>
       <c r="F3" s="3">
         <v>0</v>
       </c>
@@ -5969,6 +5975,9 @@
       <c r="D4" t="s">
         <v>93</v>
       </c>
+      <c r="E4" s="3">
+        <v>1472</v>
+      </c>
       <c r="F4" s="3">
         <v>1</v>
       </c>
@@ -5998,6 +6007,9 @@
       <c r="D5" t="s">
         <v>180</v>
       </c>
+      <c r="E5" s="3">
+        <v>662</v>
+      </c>
       <c r="F5" s="3">
         <v>0</v>
       </c>
@@ -6026,6 +6038,9 @@
       </c>
       <c r="D6" t="s">
         <v>148</v>
+      </c>
+      <c r="E6" s="3">
+        <v>551</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -6056,6 +6071,9 @@
       <c r="D7" t="s">
         <v>60</v>
       </c>
+      <c r="E7" s="3">
+        <v>549</v>
+      </c>
       <c r="F7" s="3">
         <v>0</v>
       </c>
@@ -6085,6 +6103,9 @@
       <c r="D8" t="s">
         <v>194</v>
       </c>
+      <c r="E8" s="3">
+        <v>1164</v>
+      </c>
       <c r="F8" s="3">
         <v>0</v>
       </c>
@@ -6114,6 +6135,9 @@
       <c r="D9" t="s">
         <v>199</v>
       </c>
+      <c r="E9" s="3">
+        <v>300</v>
+      </c>
       <c r="F9" s="3">
         <v>0</v>
       </c>
@@ -6142,6 +6166,9 @@
       </c>
       <c r="D10" t="s">
         <v>35</v>
+      </c>
+      <c r="E10" s="3">
+        <v>298</v>
       </c>
       <c r="F10" s="3">
         <v>0</v>
@@ -6172,6 +6199,9 @@
       <c r="D11" t="s">
         <v>113</v>
       </c>
+      <c r="E11" s="3">
+        <v>702</v>
+      </c>
       <c r="F11" s="3">
         <v>0</v>
       </c>
@@ -6201,6 +6231,9 @@
       <c r="D12" t="s">
         <v>56</v>
       </c>
+      <c r="E12" s="3">
+        <v>652</v>
+      </c>
       <c r="F12" s="3">
         <v>0</v>
       </c>
@@ -6229,6 +6262,9 @@
       </c>
       <c r="D13" t="s">
         <v>184</v>
+      </c>
+      <c r="E13" s="3">
+        <v>299</v>
       </c>
       <c r="F13" s="3">
         <v>0</v>
@@ -6259,6 +6295,9 @@
       <c r="D14" t="s">
         <v>89</v>
       </c>
+      <c r="E14" s="3">
+        <v>305</v>
+      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
@@ -6288,6 +6327,9 @@
       <c r="D15" t="s">
         <v>41</v>
       </c>
+      <c r="E15" s="3">
+        <v>652</v>
+      </c>
       <c r="F15" s="3">
         <v>0</v>
       </c>
@@ -6317,6 +6359,9 @@
       <c r="D16" t="s">
         <v>119</v>
       </c>
+      <c r="E16" s="3">
+        <v>381</v>
+      </c>
       <c r="F16" s="3">
         <v>0</v>
       </c>
@@ -6346,6 +6391,9 @@
       <c r="D17" t="s">
         <v>12</v>
       </c>
+      <c r="E17" s="3">
+        <v>1361</v>
+      </c>
       <c r="F17" s="3">
         <v>0</v>
       </c>
@@ -6375,6 +6423,9 @@
       <c r="D18" t="s">
         <v>115</v>
       </c>
+      <c r="E18" s="3">
+        <v>1162</v>
+      </c>
       <c r="F18" s="3">
         <v>1</v>
       </c>
@@ -6404,6 +6455,9 @@
       <c r="D19" t="s">
         <v>203</v>
       </c>
+      <c r="E19" s="3">
+        <v>498</v>
+      </c>
       <c r="F19" s="3">
         <v>0</v>
       </c>
@@ -6433,6 +6487,9 @@
       <c r="D20" t="s">
         <v>24</v>
       </c>
+      <c r="E20" s="3">
+        <v>599</v>
+      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
@@ -6461,6 +6518,9 @@
       </c>
       <c r="D21" t="s">
         <v>103</v>
+      </c>
+      <c r="E21" s="3">
+        <v>307</v>
       </c>
       <c r="F21" s="3">
         <v>0</v>
@@ -6491,6 +6551,9 @@
       <c r="D22" t="s">
         <v>70</v>
       </c>
+      <c r="E22" s="3">
+        <v>697</v>
+      </c>
       <c r="F22" s="3">
         <v>0</v>
       </c>
@@ -6520,6 +6583,9 @@
       <c r="D23" t="s">
         <v>18</v>
       </c>
+      <c r="E23" s="3">
+        <v>598</v>
+      </c>
       <c r="F23" s="3">
         <v>0</v>
       </c>
@@ -6549,6 +6615,9 @@
       <c r="D24" t="s">
         <v>14</v>
       </c>
+      <c r="E24" s="3">
+        <v>749</v>
+      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -6578,6 +6647,9 @@
       <c r="D25" t="s">
         <v>109</v>
       </c>
+      <c r="E25" s="3">
+        <v>437</v>
+      </c>
       <c r="F25" s="3">
         <v>0</v>
       </c>
@@ -6607,6 +6679,9 @@
       <c r="D26" t="s">
         <v>146</v>
       </c>
+      <c r="E26" s="3">
+        <v>303</v>
+      </c>
       <c r="F26" s="3">
         <v>0</v>
       </c>
@@ -6635,6 +6710,9 @@
       </c>
       <c r="D27" t="s">
         <v>186</v>
+      </c>
+      <c r="E27" s="3">
+        <v>438</v>
       </c>
       <c r="F27" s="3">
         <v>0</v>
@@ -6665,6 +6743,9 @@
       <c r="D28" t="s">
         <v>158</v>
       </c>
+      <c r="E28" s="3">
+        <v>567</v>
+      </c>
       <c r="F28" s="3">
         <v>0</v>
       </c>
@@ -6694,6 +6775,9 @@
       <c r="D29" t="s">
         <v>196</v>
       </c>
+      <c r="E29" s="3">
+        <v>738</v>
+      </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
@@ -6722,6 +6806,9 @@
       </c>
       <c r="D30" t="s">
         <v>101</v>
+      </c>
+      <c r="E30" s="3">
+        <v>344</v>
       </c>
       <c r="F30" s="3">
         <v>0</v>
@@ -6752,6 +6839,9 @@
       <c r="D31" t="s">
         <v>172</v>
       </c>
+      <c r="E31" s="3">
+        <v>825</v>
+      </c>
       <c r="F31" s="3">
         <v>0</v>
       </c>
@@ -6781,6 +6871,9 @@
       <c r="D32" t="s">
         <v>29</v>
       </c>
+      <c r="E32" s="3">
+        <v>1255</v>
+      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -6810,6 +6903,9 @@
       <c r="D33" t="s">
         <v>190</v>
       </c>
+      <c r="E33" s="3">
+        <v>303</v>
+      </c>
       <c r="F33" s="3">
         <v>0</v>
       </c>
@@ -6838,6 +6934,9 @@
       </c>
       <c r="D34" t="s">
         <v>130</v>
+      </c>
+      <c r="E34" s="3">
+        <v>298</v>
       </c>
       <c r="F34" s="3">
         <v>0</v>
@@ -6868,6 +6967,9 @@
       <c r="D35" t="s">
         <v>170</v>
       </c>
+      <c r="E35" s="3">
+        <v>1489</v>
+      </c>
       <c r="F35" s="3">
         <v>0</v>
       </c>
@@ -6897,6 +6999,9 @@
       <c r="D36" t="s">
         <v>87</v>
       </c>
+      <c r="E36" s="3">
+        <v>1037</v>
+      </c>
       <c r="F36" s="3">
         <v>0</v>
       </c>
@@ -6926,6 +7031,9 @@
       <c r="D37" t="s">
         <v>51</v>
       </c>
+      <c r="E37" s="3">
+        <v>633</v>
+      </c>
       <c r="F37" s="3">
         <v>0</v>
       </c>
@@ -6955,6 +7063,9 @@
       <c r="D38" t="s">
         <v>95</v>
       </c>
+      <c r="E38" s="3">
+        <v>396</v>
+      </c>
       <c r="F38" s="3">
         <v>0</v>
       </c>
@@ -6984,6 +7095,9 @@
       <c r="D39" t="s">
         <v>43</v>
       </c>
+      <c r="E39" s="3">
+        <v>884</v>
+      </c>
       <c r="F39" s="3">
         <v>1</v>
       </c>
@@ -7012,6 +7126,9 @@
       </c>
       <c r="D40" t="s">
         <v>85</v>
+      </c>
+      <c r="E40" s="3">
+        <v>298</v>
       </c>
       <c r="F40" s="3">
         <v>0</v>
@@ -7042,6 +7159,9 @@
       <c r="D41" t="s">
         <v>156</v>
       </c>
+      <c r="E41" s="3">
+        <v>1217</v>
+      </c>
       <c r="F41" s="3">
         <v>0</v>
       </c>
@@ -7071,6 +7191,9 @@
       <c r="D42" t="s">
         <v>132</v>
       </c>
+      <c r="E42" s="3">
+        <v>511</v>
+      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -7099,6 +7222,9 @@
       </c>
       <c r="D43" t="s">
         <v>39</v>
+      </c>
+      <c r="E43" s="3">
+        <v>352</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -7129,6 +7255,9 @@
       <c r="D44" t="s">
         <v>209</v>
       </c>
+      <c r="E44" s="3">
+        <v>1015</v>
+      </c>
       <c r="F44" s="3">
         <v>0</v>
       </c>
@@ -7158,6 +7287,9 @@
       <c r="D45" t="s">
         <v>20</v>
       </c>
+      <c r="E45" s="3">
+        <v>845</v>
+      </c>
       <c r="F45" s="3">
         <v>0</v>
       </c>
@@ -7187,6 +7319,9 @@
       <c r="D46" t="s">
         <v>77</v>
       </c>
+      <c r="E46" s="3">
+        <v>383</v>
+      </c>
       <c r="F46" s="3">
         <v>0</v>
       </c>
@@ -7216,6 +7351,9 @@
       <c r="D47" t="s">
         <v>64</v>
       </c>
+      <c r="E47" s="3">
+        <v>668</v>
+      </c>
       <c r="F47" s="3">
         <v>0</v>
       </c>
@@ -7245,6 +7383,9 @@
       <c r="D48" t="s">
         <v>150</v>
       </c>
+      <c r="E48" s="3">
+        <v>438</v>
+      </c>
       <c r="F48" s="3">
         <v>0</v>
       </c>
@@ -7274,6 +7415,9 @@
       <c r="D49" t="s">
         <v>72</v>
       </c>
+      <c r="E49" s="3">
+        <v>738</v>
+      </c>
       <c r="F49" s="3">
         <v>0</v>
       </c>
@@ -7303,6 +7447,9 @@
       <c r="D50" t="s">
         <v>140</v>
       </c>
+      <c r="E50" s="3">
+        <v>351</v>
+      </c>
       <c r="F50" s="3">
         <v>0</v>
       </c>
@@ -7331,6 +7478,9 @@
       </c>
       <c r="D51" t="s">
         <v>126</v>
+      </c>
+      <c r="E51" s="3">
+        <v>299</v>
       </c>
       <c r="F51" s="3">
         <v>0</v>
@@ -7361,6 +7511,9 @@
       <c r="D52" t="s">
         <v>33</v>
       </c>
+      <c r="E52" s="3">
+        <v>1451</v>
+      </c>
       <c r="F52" s="3">
         <v>1</v>
       </c>
@@ -7389,6 +7542,9 @@
       </c>
       <c r="D53" t="s">
         <v>164</v>
+      </c>
+      <c r="E53" s="3">
+        <v>298</v>
       </c>
       <c r="F53" s="3">
         <v>0</v>
@@ -7419,6 +7575,9 @@
       <c r="D54" t="s">
         <v>111</v>
       </c>
+      <c r="E54" s="3">
+        <v>529</v>
+      </c>
       <c r="F54" s="3">
         <v>0</v>
       </c>
@@ -7448,6 +7607,9 @@
       <c r="D55" t="s">
         <v>91</v>
       </c>
+      <c r="E55" s="3">
+        <v>377</v>
+      </c>
       <c r="F55" s="3">
         <v>0</v>
       </c>
@@ -7477,6 +7639,9 @@
       <c r="D56" t="s">
         <v>144</v>
       </c>
+      <c r="E56" s="3">
+        <v>798</v>
+      </c>
       <c r="F56" s="3">
         <v>0</v>
       </c>
@@ -7506,6 +7671,9 @@
       <c r="D57" t="s">
         <v>117</v>
       </c>
+      <c r="E57" s="3">
+        <v>810</v>
+      </c>
       <c r="F57" s="3">
         <v>1</v>
       </c>
@@ -7535,6 +7703,9 @@
       <c r="D58" t="s">
         <v>207</v>
       </c>
+      <c r="E58" s="3">
+        <v>697</v>
+      </c>
       <c r="F58" s="3">
         <v>0</v>
       </c>
@@ -7564,6 +7735,9 @@
       <c r="D59" t="s">
         <v>178</v>
       </c>
+      <c r="E59" s="3">
+        <v>306</v>
+      </c>
       <c r="F59" s="3">
         <v>0</v>
       </c>
@@ -7592,6 +7766,9 @@
       </c>
       <c r="D60" t="s">
         <v>74</v>
+      </c>
+      <c r="E60" s="3">
+        <v>397</v>
       </c>
       <c r="F60" s="3">
         <v>0</v>
@@ -7622,6 +7799,9 @@
       <c r="D61" t="s">
         <v>107</v>
       </c>
+      <c r="E61" s="3">
+        <v>620</v>
+      </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
@@ -7651,6 +7831,9 @@
       <c r="D62" t="s">
         <v>99</v>
       </c>
+      <c r="E62" s="3">
+        <v>626</v>
+      </c>
       <c r="F62" s="3">
         <v>0</v>
       </c>
@@ -7680,6 +7863,9 @@
       <c r="D63" t="s">
         <v>37</v>
       </c>
+      <c r="E63" s="3">
+        <v>536</v>
+      </c>
       <c r="F63" s="3">
         <v>0</v>
       </c>
@@ -7708,6 +7894,9 @@
       </c>
       <c r="D64" t="s">
         <v>47</v>
+      </c>
+      <c r="E64" s="3">
+        <v>1600</v>
       </c>
       <c r="F64" s="3">
         <v>0</v>
@@ -7738,6 +7927,9 @@
       <c r="D65" t="s">
         <v>83</v>
       </c>
+      <c r="E65" s="3">
+        <v>1547</v>
+      </c>
       <c r="F65" s="3">
         <v>1</v>
       </c>
@@ -7767,6 +7959,9 @@
       <c r="D66" t="s">
         <v>27</v>
       </c>
+      <c r="E66" s="3">
+        <v>302</v>
+      </c>
       <c r="F66" s="3">
         <v>0</v>
       </c>
@@ -7795,6 +7990,9 @@
       </c>
       <c r="D67" t="s">
         <v>166</v>
+      </c>
+      <c r="E67" s="3">
+        <v>300</v>
       </c>
       <c r="F67" s="3">
         <v>0</v>
@@ -7825,6 +8023,9 @@
       <c r="D68" t="s">
         <v>128</v>
       </c>
+      <c r="E68" s="3">
+        <v>666</v>
+      </c>
       <c r="F68" s="3">
         <v>0</v>
       </c>
@@ -7854,6 +8055,9 @@
       <c r="D69" t="s">
         <v>81</v>
       </c>
+      <c r="E69" s="3">
+        <v>425</v>
+      </c>
       <c r="F69" s="3">
         <v>0</v>
       </c>
@@ -7882,6 +8086,9 @@
       </c>
       <c r="D70" t="s">
         <v>139</v>
+      </c>
+      <c r="E70" s="3">
+        <v>304</v>
       </c>
       <c r="F70" s="3">
         <v>0</v>
@@ -7912,6 +8119,9 @@
       <c r="D71" t="s">
         <v>31</v>
       </c>
+      <c r="E71" s="3">
+        <v>301</v>
+      </c>
       <c r="F71" s="3">
         <v>0</v>
       </c>
@@ -7941,6 +8151,9 @@
       <c r="D72" t="s">
         <v>54</v>
       </c>
+      <c r="E72" s="3">
+        <v>303</v>
+      </c>
       <c r="F72" s="3">
         <v>0</v>
       </c>
@@ -7970,6 +8183,9 @@
       <c r="D73" t="s">
         <v>58</v>
       </c>
+      <c r="E73" s="3">
+        <v>741</v>
+      </c>
       <c r="F73" s="3">
         <v>0</v>
       </c>
@@ -7998,6 +8214,9 @@
       </c>
       <c r="D74" t="s">
         <v>105</v>
+      </c>
+      <c r="E74" s="3">
+        <v>298</v>
       </c>
       <c r="F74" s="3">
         <v>0</v>
@@ -8028,6 +8247,9 @@
       <c r="D75" t="s">
         <v>154</v>
       </c>
+      <c r="E75" s="3">
+        <v>1842</v>
+      </c>
       <c r="F75" s="3">
         <v>0</v>
       </c>
@@ -8057,6 +8279,9 @@
       <c r="D76" t="s">
         <v>198</v>
       </c>
+      <c r="E76" s="3">
+        <v>301</v>
+      </c>
       <c r="F76" s="3">
         <v>0</v>
       </c>
@@ -8085,6 +8310,9 @@
       </c>
       <c r="D77" t="s">
         <v>201</v>
+      </c>
+      <c r="E77" s="3">
+        <v>369</v>
       </c>
       <c r="F77" s="3">
         <v>0</v>
@@ -8115,6 +8343,9 @@
       <c r="D78" t="s">
         <v>160</v>
       </c>
+      <c r="E78" s="3">
+        <v>925</v>
+      </c>
       <c r="F78" s="3">
         <v>0</v>
       </c>
@@ -8143,6 +8374,9 @@
       </c>
       <c r="D79" t="s">
         <v>142</v>
+      </c>
+      <c r="E79" s="3">
+        <v>396</v>
       </c>
       <c r="F79" s="3">
         <v>0</v>
@@ -8173,6 +8407,9 @@
       <c r="D80" t="s">
         <v>182</v>
       </c>
+      <c r="E80" s="3">
+        <v>718</v>
+      </c>
       <c r="F80" s="3">
         <v>1</v>
       </c>
@@ -8201,6 +8438,9 @@
       </c>
       <c r="D81" t="s">
         <v>45</v>
+      </c>
+      <c r="E81" s="3">
+        <v>306</v>
       </c>
       <c r="F81" s="3">
         <v>0</v>
@@ -8231,6 +8471,9 @@
       <c r="D82" t="s">
         <v>205</v>
       </c>
+      <c r="E82" s="3">
+        <v>471</v>
+      </c>
       <c r="F82" s="3">
         <v>0</v>
       </c>
@@ -8260,6 +8503,9 @@
       <c r="D83" t="s">
         <v>8</v>
       </c>
+      <c r="E83" s="3">
+        <v>625</v>
+      </c>
       <c r="F83" s="3">
         <v>0</v>
       </c>
@@ -8288,6 +8534,9 @@
       </c>
       <c r="D84" t="s">
         <v>137</v>
+      </c>
+      <c r="E84" s="3">
+        <v>804</v>
       </c>
       <c r="F84" s="3">
         <v>0</v>
@@ -8318,6 +8567,9 @@
       <c r="D85" t="s">
         <v>192</v>
       </c>
+      <c r="E85" s="3">
+        <v>1576</v>
+      </c>
       <c r="F85" s="3">
         <v>0</v>
       </c>
@@ -8347,6 +8599,9 @@
       <c r="D86" t="s">
         <v>79</v>
       </c>
+      <c r="E86" s="3">
+        <v>300</v>
+      </c>
       <c r="F86" s="3">
         <v>0</v>
       </c>
@@ -8375,6 +8630,9 @@
       </c>
       <c r="D87" t="s">
         <v>22</v>
+      </c>
+      <c r="E87" s="3">
+        <v>303</v>
       </c>
       <c r="F87" s="3">
         <v>0</v>
@@ -8405,6 +8663,9 @@
       <c r="D88" t="s">
         <v>97</v>
       </c>
+      <c r="E88" s="3">
+        <v>910</v>
+      </c>
       <c r="F88" s="3">
         <v>0</v>
       </c>
@@ -8434,6 +8695,9 @@
       <c r="D89" t="s">
         <v>135</v>
       </c>
+      <c r="E89" s="3">
+        <v>427</v>
+      </c>
       <c r="F89" s="3">
         <v>0</v>
       </c>
@@ -8463,6 +8727,9 @@
       <c r="D90" t="s">
         <v>62</v>
       </c>
+      <c r="E90" s="3">
+        <v>484</v>
+      </c>
       <c r="F90" s="3">
         <v>0</v>
       </c>
@@ -8492,6 +8759,9 @@
       <c r="D91" t="s">
         <v>168</v>
       </c>
+      <c r="E91" s="3">
+        <v>799</v>
+      </c>
       <c r="F91" s="3">
         <v>1</v>
       </c>
@@ -8521,6 +8791,9 @@
       <c r="D92" t="s">
         <v>10</v>
       </c>
+      <c r="E92" s="3">
+        <v>690</v>
+      </c>
       <c r="F92" s="3">
         <v>0</v>
       </c>
@@ -8550,6 +8823,9 @@
       <c r="D93" t="s">
         <v>68</v>
       </c>
+      <c r="E93" s="3">
+        <v>985</v>
+      </c>
       <c r="F93" s="3">
         <v>1</v>
       </c>
@@ -8579,6 +8855,9 @@
       <c r="D94" t="s">
         <v>211</v>
       </c>
+      <c r="E94" s="3">
+        <v>663</v>
+      </c>
       <c r="F94" s="3">
         <v>0</v>
       </c>
@@ -8607,6 +8886,9 @@
       </c>
       <c r="D95" t="s">
         <v>152</v>
+      </c>
+      <c r="E95" s="3">
+        <v>1209</v>
       </c>
       <c r="F95" s="3">
         <v>0</v>
@@ -8637,6 +8919,9 @@
       <c r="D96" t="s">
         <v>122</v>
       </c>
+      <c r="E96" s="3">
+        <v>532</v>
+      </c>
       <c r="F96" s="3">
         <v>1</v>
       </c>
@@ -8666,6 +8951,9 @@
       <c r="D97" t="s">
         <v>176</v>
       </c>
+      <c r="E97" s="3">
+        <v>563</v>
+      </c>
       <c r="F97" s="3">
         <v>0</v>
       </c>
@@ -8695,6 +8983,9 @@
       <c r="D98" t="s">
         <v>49</v>
       </c>
+      <c r="E98" s="3">
+        <v>522</v>
+      </c>
       <c r="F98" s="3">
         <v>0</v>
       </c>
@@ -8724,6 +9015,9 @@
       <c r="D99" t="s">
         <v>162</v>
       </c>
+      <c r="E99" s="3">
+        <v>298</v>
+      </c>
       <c r="F99" s="3">
         <v>0</v>
       </c>
@@ -8752,6 +9046,9 @@
       </c>
       <c r="D100" t="s">
         <v>124</v>
+      </c>
+      <c r="E100" s="3">
+        <v>299</v>
       </c>
       <c r="F100" s="3">
         <v>0</v>
@@ -8781,6 +9078,9 @@
       </c>
       <c r="D101" t="s">
         <v>174</v>
+      </c>
+      <c r="E101" s="3">
+        <v>366</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
